--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>470</v>
+        <v>1654</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_cart_rules_1125.xlsx
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1654</v>
+        <v>11681</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
